--- a/Traceability_Matrix.xlsx
+++ b/Traceability_Matrix.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,27 +461,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>URS-001</t>
+          <t>URS-101</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>The washer shall complete a validated cleaning cycle.</t>
+          <t>The washer shall alarm upon cycle failure.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Cleaning</t>
+          <t>Alarm</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Major</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>OQ / PQ</t>
+          <t>OQ</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,7 +496,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>OQ-001, FAT-001, SAT-001, IQ-001</t>
+          <t>OQ-001, IQ-001, FAT-001, SAT-001</t>
         </is>
       </c>
     </row>
@@ -508,22 +508,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>The washer shall alarm upon cycle failure.</t>
+          <t>The washer shall complete a validated cleaning cycle.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Alarm</t>
+          <t>Cleaning</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Major</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>OQ</t>
+          <t>OQ / PQ</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -541,12 +541,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>The washer shall record cycle data.</t>
+          <t>The washer shall alarm upon cycle failure.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Data Integrity</t>
+          <t>Alarm</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>CSV / OQ</t>
+          <t>OQ</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -574,22 +574,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>The system shall maintain pressure during operation.</t>
+          <t>The washer shall record cycle data.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Environmental</t>
+          <t>Data Integrity</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Major</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>OQ</t>
+          <t>CSV / OQ</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -607,17 +607,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>The safety interlock shall prevent unsafe operation.</t>
+          <t>The system shall maintain pressure during operation.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Safety</t>
+          <t>Environmental</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Major</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -640,30 +640,261 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>The safety interlock shall prevent unsafe operation.</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Safety</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>OQ</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>URS-007</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
           <t>The operator shall complete training before use.</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Operational</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>Minor</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>SOP / Training</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>URS-001</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>The washer shall complete a validated cleaning cycle.</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Cleaning</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>OQ / PQ</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>URS-002</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>The washer shall alarm upon cycle failure.</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Alarm</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>OQ</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>URS-003</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>The washer shall record cycle data.</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Data Integrity</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>CSV / OQ</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>URS-004</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>The system shall maintain pressure during operation.</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Environmental</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>OQ</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>URS-005</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>The safety interlock shall prevent unsafe operation.</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Safety</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>OQ</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>URS-006</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>The operator shall complete training before use.</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Operational</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>SOP / Training</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Traceability_Matrix.xlsx
+++ b/Traceability_Matrix.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -697,204 +697,6 @@
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>URS-001</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>The washer shall complete a validated cleaning cycle.</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Cleaning</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Major</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>OQ / PQ</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>URS-002</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>The washer shall alarm upon cycle failure.</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Alarm</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>OQ</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>URS-003</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>The washer shall record cycle data.</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Data Integrity</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>CSV / OQ</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>URS-004</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>The system shall maintain pressure during operation.</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Environmental</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Major</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>OQ</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>URS-005</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>The safety interlock shall prevent unsafe operation.</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Safety</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>OQ</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>URS-006</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>The operator shall complete training before use.</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Operational</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Minor</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>SOP / Training</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Traceability_Matrix.xlsx
+++ b/Traceability_Matrix.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,27 +461,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>URS-101</t>
+          <t>URS-001</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>The washer shall alarm upon cycle failure.</t>
+          <t>The washer shall complete a validated cleaning cycle.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Alarm</t>
+          <t>Cleaning</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Major</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>OQ</t>
+          <t>OQ / PQ</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -508,22 +508,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>The washer shall complete a validated cleaning cycle.</t>
+          <t>The washer shall alarm upon cycle failure.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Cleaning</t>
+          <t>Alarm</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Major</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>OQ / PQ</t>
+          <t>OQ</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -541,12 +541,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>The washer shall alarm upon cycle failure.</t>
+          <t>The washer shall record cycle data.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Alarm</t>
+          <t>Data Integrity</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>OQ</t>
+          <t>CSV / OQ</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -574,22 +574,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>The washer shall record cycle data.</t>
+          <t>The system shall maintain pressure during operation.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Data Integrity</t>
+          <t>Environmental</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Major</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>CSV / OQ</t>
+          <t>OQ</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -607,17 +607,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>The system shall maintain pressure during operation.</t>
+          <t>The safety interlock shall prevent unsafe operation.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Environmental</t>
+          <t>Safety</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Major</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -640,22 +640,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>The safety interlock shall prevent unsafe operation.</t>
+          <t>The operator shall complete training before use.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Safety</t>
+          <t>Operational</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Minor</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>OQ</t>
+          <t>SOP / Training</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -664,39 +664,6 @@
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>URS-007</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>The operator shall complete training before use.</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Operational</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Minor</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>SOP / Training</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Traceability_Matrix.xlsx
+++ b/Traceability_Matrix.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,22 +466,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>The washer shall complete a validated cleaning cycle.</t>
+          <t>It shall be the contractor’s responsibility to be knowledgeable of the latest applicable United States standards and codes during design and fabrication.  In the event of a conflict between referenced codes, standards, and specifications, the most stringent shall apply and the Contractor shall notify Bachem Americas, Inc. of resolution.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Cleaning</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Major</t>
+          <t>Minor</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>OQ / PQ</t>
+          <t>Commissioning / IQ / OQ</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -508,22 +508,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>The washer shall alarm upon cycle failure.</t>
+          <t>A turnover package shall be supplied to Bachem Americas, Inc. upon successful construction and factory testing completion of the upgraded components.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Alarm</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Minor</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>OQ</t>
+          <t>Commissioning / IQ / OQ</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -541,22 +541,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>The washer shall record cycle data.</t>
+          <t>The following table summarizes minimum differential pressure requirements between rooms. EU GMP 2020 Annex 1 provides the basis for these values and gives a guidance minimum differential pressure of 10 pascals (0.04 inches of water) between different room classifications. Differential pressure gauges shall be greater than or equal to the values shown in the Minimum Differential Pressure (inches of water column). Note: for transition rooms that have a split classification, the entire room is tested against the stricter grade.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Data Integrity</t>
+          <t>Environmental</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Major</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>CSV / OQ</t>
+          <t>OQ</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -565,105 +565,6 @@
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>URS-004</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>The system shall maintain pressure during operation.</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Environmental</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Major</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>OQ</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>URS-005</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>The safety interlock shall prevent unsafe operation.</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Safety</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>OQ</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>URS-006</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>The operator shall complete training before use.</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Operational</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Minor</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>SOP / Training</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Traceability_Matrix.xlsx
+++ b/Traceability_Matrix.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:N85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,17 +444,47 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>DQ</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>FAT</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Commissioning</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>IQ</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>OQ</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>PQ</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Verified By</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Trace Links</t>
         </is>
       </c>
     </row>
@@ -466,37 +496,51 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>It shall be the contractor’s responsibility to be knowledgeable of the latest applicable United States standards and codes during design and fabrication.  In the event of a conflict between referenced codes, standards, and specifications, the most stringent shall apply and the Contractor shall notify Bachem Americas, Inc. of resolution.</t>
+          <t>The occupant limit for the pre-gown room (606) shall be 1 personnel.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Occupancy Control</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Minor</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Commissioning / IQ / OQ</t>
+          <t>Ensure compliance with occupancy limits to maintain controlled environment integrity.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>TEST-001</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>TEST-002</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>TEST-003</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>OQ-001</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>OQ-001, IQ-001, FAT-001, SAT-001</t>
         </is>
       </c>
     </row>
@@ -508,30 +552,60 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>A turnover package shall be supplied to Bachem Americas, Inc. upon successful construction and factory testing completion of the upgraded components.</t>
+          <t>The occupant limit for the gown room (607) shall be 1 personnel.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Facility Design and Control</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Minor</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Commissioning / IQ / OQ</t>
+          <t>Ensure compliance with gowning procedures and personnel limits.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
+          <t>TEST-004</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>TEST-005</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>TEST-006</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>TEST-007</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>TEST-008</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>TEST-009</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -541,30 +615,4619 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>The following table summarizes minimum differential pressure requirements between rooms. EU GMP 2020 Annex 1 provides the basis for these values and gives a guidance minimum differential pressure of 10 pascals (0.04 inches of water) between different room classifications. Differential pressure gauges shall be greater than or equal to the values shown in the Minimum Differential Pressure (inches of water column). Note: for transition rooms that have a split classification, the entire room is tested against the stricter grade.</t>
+          <t>The occupant limit for the clean room (609) shall be 2 personnel.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Environmental</t>
+          <t>Clean Room Occupancy</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Major</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>OQ</t>
+          <t>Ensure compliance with occupancy limits during operations.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
+          <t>TEST-010</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>TEST-011</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>TEST-012</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>URS-004</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>The occupant limit for the equipment drying pass room (610) shall be 1 personnel.</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Occupancy Limit</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Monitoring of personnel access and occupancy in the drying pass room.</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>TEST-013</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>TEST-014</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>TEST-015</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>TEST-016</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>TEST-017</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>TEST-018</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>URS-005</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>The occupant limit for the equipment pass through room (611) shall be 1 personnel.</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Facility Design Requirement</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Ensure compliance with occupancy limits during operational procedures.</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>TEST-019</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>TEST-020</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>TEST-021</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>TEST-022</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>URS-006</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Supply side ventilation to classified cleanroom suites shall have terminal HEPA filtration installed, capable of</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>HVAC System Design</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>HEPA filter integrity testing and airflow validation</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>TEST-023</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>TEST-024</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>TEST-025</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>TEST-026</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>TEST-027</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>TEST-028</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>URS-007</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>The system shall maintain non-viable airborne particulate conditions within Grade C and Grade D (per EU</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Environmental Control</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Monitoring and testing of airborne particulate levels in Grade C and Grade D areas.</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>TEST-029</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>TEST-030</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>TEST-031</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>TEST-032</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>TEST-033</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>URS-008</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>The system shall maintain viable airborne particulate conditions within Grade C and Grade D (per EU GMP</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Environmental Control</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Monitoring and testing of airborne particulate levels in Grade C and Grade D areas.</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>TEST-034</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>TEST-035</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>TEST-036</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>TEST-037</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>TEST-038</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>URS-009</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>The system shall maintain the air changes per hour according to Appendix C.</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Environmental Control</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Monitoring and recording of air changes per hour (ACH) must be implemented and validated.</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>TEST-039</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>TEST-040</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>TEST-041</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>TEST-042</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>TEST-043</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>URS-010</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>The washroom suite shall be clearly labeled.</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Labeling and Identification</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Visual inspection and documentation review</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>TEST-044</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>TEST-045</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>TEST-046</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>URS-011</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Utility connections requiring less frequent use shall sit within 72” from the floor.</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Utility Connection Design</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Visual inspection and measurement of utility connections' height from the floor.</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>TEST-047</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>TEST-048</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>TEST-049</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>TEST-050</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>TEST-051</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>TEST-052</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>TEST-053</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>URS-012</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>All rooms shall be equipped with a fire protection system.</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Safety and Compliance</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Fire protection system functionality and compliance with local regulations.</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>TEST-054</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>TEST-055</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>TEST-056</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>TEST-057</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>TEST-058</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>TEST-059</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>URS-013</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>All cleanroom light fixtures shall be enclosed to be protected against the elements in the room.</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Cleanroom Environment Control</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Visual inspection and functional testing of light fixtures to ensure they are properly enclosed and operational.</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>TEST-060</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>TEST-061</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>TEST-062</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>TEST-063</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>URS-014</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>The Decontamination Washer Suite shall include the CNC Washroom (Room 605).</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Cleaning Validation</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Cleaning validation must confirm the effectiveness of the decontamination process for all product contact equipment in the CNC Washroom.</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>TEST-064</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>TEST-065</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>TEST-066</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>TEST-067</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>URS-015</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>The Decontamination Washer Suite shall include the Pre-Gown Room (Room 606).</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Facility Design</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Ensure that the Pre-Gown Room is designed to prevent contamination and facilitate proper gowning procedures.</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>TEST-068</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>TEST-069</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>TEST-070</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>TEST-071</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>TEST-072</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>TEST-073</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>URS-016</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>The Decontamination Washer Suite shall include the Gown Room (Room 607).</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Facility Design and Equipment</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Ensure that the Decontamination Washer Suite, including the Gown Room, is designed to prevent cross-contamination and maintain cleanliness.</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>TEST-074</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>TEST-075</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>TEST-076</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>TEST-077</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>URS-017</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>The Decontamination Washer Suite shall include the Utility Room (Room 608).</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Facility Design and Utilities</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Ensure that the Utility Room (Room 608) is designed and equipped to support the decontamination process effectively.</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>TEST-078</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>TEST-079</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>TEST-080</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>TEST-081</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>TEST-082</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>TEST-083</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>TEST-084</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>URS-018</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>The Decontamination Washer Suite shall include the Glassware Package (Room 609).</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Cleaning Validation</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Cleaning validation must confirm the effectiveness of the decontamination process for the Glassware Package in Room 609.</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>TEST-085</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>TEST-086</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>TEST-087</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>TEST-088</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>URS-019</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>The Decontamination Washer Suite shall include the Equipment Drying Room (Room 610).</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Cleaning and Decontamination</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Cleaning validation must confirm the effectiveness of the decontamination process for all product contact equipment.</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>TEST-089</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>TEST-090</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>TEST-091</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>TEST-092</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>URS-020</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>The Decontamination Washer Suite shall include the Equipment Pass Through (Room 611).</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Cleaning and Decontamination</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Cleaning validation must be performed to confirm the effectiveness of the decontamination process for the Equipment Pass Through.</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>TEST-093</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>TEST-094</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>TEST-095</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>TEST-096</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>URS-021</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>The Decontamination Washer Suite shall include the CNC Clean Storage Room (Room 612).</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Cleaning Validation</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Cleaning validation must confirm the effectiveness of the cleaning procedure for all product contact equipment, including the CNC Clean Storage Room.</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>TEST-097</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>TEST-098</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>TEST-099</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>TEST-100</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>URS-022</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>The unloading chamber door for the decontamination washer shall be accessible.</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Accessibility and Maintenance</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Visual inspection and functional testing of the unloading chamber door to ensure it is accessible and operational.</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>TEST-101</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>TEST-102</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>TEST-103</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>TEST-104</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>URS-023</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>The Decontamination Washer Suite shall have minimized dead spaces such as joints, crevices, and cavities in which the product or moisture can settle and lead to cross-contamination or germination.</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Design Requirement</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Visual inspection and cleaning validation protocols should confirm the absence of dead spaces.</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>TEST-105</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>TEST-106</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>TEST-107</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>TEST-108</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>URS-024</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>All cleanroom elements, components and exposed surfaces shall be designed in such a way that the surfaces are level and smooth.</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Design Requirement</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Visual inspection and surface testing for smoothness and levelness.</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>TEST-109</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>TEST-110</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>TEST-111</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>TEST-112</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>URS-025</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>All cleanroom elements, components and exposed surfaces shall be designed in such a way that the surfaces are airtight or sealed.</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Design Requirement</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Design review and testing for airtightness and sealing integrity.</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>TEST-113</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>TEST-114</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>TEST-115</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>URS-026</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>All cleanroom elements, components and exposed surfaces shall be designed in such a way that the surfaces are free of protruding sharp edges.</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Design Requirement</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Design review and inspection of cleanroom elements and surfaces.</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>TEST-116</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>TEST-117</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>TEST-118</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>URS-027</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>All cleanroom elements, components and exposed surfaces shall be designed in such a way that the surfaces are non-particulate generating under normal conditions with regular maintenance.</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Design Requirement</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Design reviews and surface testing for particulate generation.</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>TEST-119</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>TEST-120</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>TEST-121</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>URS-028</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>The rooms shall have a boundary that distinguishes between higher and lower classification.</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Facility Design</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Design Qualification (DQ) to confirm that the room boundaries are appropriately defined and compliant with classification requirements.</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>TEST-122</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>TEST-123</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>TEST-124</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>TEST-125</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>TEST-126</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>TEST-127</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>URS-029</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>The surfaces of the cleanroom and components shall be resistant against Bachem approved cleaning solutions and sanitizing agents.</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Cleaning and Sanitization</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Surface material testing against Bachem approved cleaning solutions and sanitizing agents.</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>TEST-128</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>TEST-129</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>TEST-130</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>TEST-131</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>URS-030</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Clean room walls shall be dry wall.</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Facility Design</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Visual inspection and documentation of installation.</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>TEST-132</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>TEST-133</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>TEST-134</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>TEST-135</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>URS-031</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Ceiling panels shall have the same engineered features as the wall panels, with pre-cut openings able to accommodate the installation of light fixtures, HEPA filters, etc.</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Facility Design</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Ensure that ceiling panels are designed and manufactured to the same specifications as wall panels, including pre-cut openings.</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>TEST-136</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>TEST-137</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>TEST-138</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>URS-032</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>All joints shall be flush, smooth and cleanable.</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Design Requirement</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Visual inspection and cleaning validation</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>TEST-139</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>URS-033</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>All corners between walls and from walls to permanent equipment fixtures in the space shall be coved.</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Facility Design</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Visual inspection and measurement of coved corners</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>TEST-140</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>TEST-141</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>TEST-142</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>URS-034</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>All wall surfaces (including joints, seals, etc.) shall not emit particulates.</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Environmental Control</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Visual inspection and particulate monitoring</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>TEST-143</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>TEST-144</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>TEST-145</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>TEST-146</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>TEST-147</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>TEST-148</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>URS-035</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>All circuits entering and leaving shall be provided with grounding.</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Electrical Safety</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Visual inspection and testing of grounding connections</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>TEST-149</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>TEST-150</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>TEST-151</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>TEST-152</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>TEST-153</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>TEST-154</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>TEST-155</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>URS-036</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>The clearance height from the floor to the bottom of the clean room suspended ceiling shall be a minimum of 8ft.</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Facility Design</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Measurement of clearance height from the floor to the bottom of the clean room suspended ceiling.</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>TEST-156</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>TEST-157</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>TEST-158</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>URS-037</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>The cleanroom light fixtures shall be installed flush with the ceiling.</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Facility Design</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Visual inspection and cleaning validation of the area around the light fixtures.</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>TEST-159</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>TEST-160</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>TEST-161</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>TEST-162</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>URS-038</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Light fixtures which are suitable for cleanroom operations shall be resistant against humidity.</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Testing for humidity resistance and compliance with cleanroom standards.</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>TEST-163</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>TEST-164</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>TEST-165</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>TEST-166</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>TEST-167</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>TEST-168</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>URS-039</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>All floors shall be coated with a static-dissipative epoxy.</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Facility Design</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Visual inspection and testing of static-dissipative properties.</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>TEST-169</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>TEST-170</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>TEST-171</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>URS-040</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Coving shall be provided on wall connections.</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Facility Design</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Visual inspection and measurement of coving installation.</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>TEST-172</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>TEST-173</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>TEST-174</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>TEST-175</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>URS-041</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>The total coving piece shall rise up at least 2”.</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Design Requirement</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Physical measurement of the coving piece to ensure it rises at least 2 inches.</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>TEST-176</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>TEST-177</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>TEST-178</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>URS-042</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>The coving radius shall be 1 to 1.25”.</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Facility Design</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Visual inspection and measurement of coving radius</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>TEST-179</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>TEST-180</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>TEST-181</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>URS-043</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Doors shall be 1- or 2-winged, with three door hinges and without a door saddle.</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Facility Design</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Visual inspection and functional testing of door operation.</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>TEST-182</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>TEST-183</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>TEST-184</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>URS-044</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Every clean room door shall have an automatic door lock and shall be equipped with a window.</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Facility Design</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Visual inspection and functional testing of the automatic door lock and window integrity.</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>TEST-185</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>TEST-186</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>TEST-187</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>URS-045</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>All doors shall be equipped with an elastic door frame seal installed circumferentially on three sides.</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Facility Design and Maintenance</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Visual inspection and functional testing of door seals.</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>TEST-188</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>TEST-189</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>TEST-190</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>URS-046</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Sealing with the floor shall be achieved with a drop-down seal.</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Equipment Qualification</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>The drop-down seal must be verified for its effectiveness in maintaining the integrity of the packaging.</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>TEST-191</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>TEST-192</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>TEST-193</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>TEST-194</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>TEST-195</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>TEST-196</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>URS-047</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>The doors shall be adapted to the adjacent cleanroom walls.</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Facility Design</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Visual inspection and measurement of door fit and sealing against cleanroom walls.</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>TEST-197</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>TEST-198</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>TEST-199</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>TEST-200</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>TEST-201</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>TEST-202</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>URS-048</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>The doors shall be installed flushed to the adjacent cleanroom walls.</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Design Requirement</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Visual inspection and measurement to ensure doors are flush with adjacent cleanroom walls.</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>TEST-203</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>TEST-204</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>TEST-205</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>URS-049</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>The gap between the bottom of the door and the top edge of the finished floor shall be between 3 and 5 mm.</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Facility Design</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Measurement of the gap using appropriate tools (e.g., calipers or gap gauges) to ensure compliance with specified dimensions.</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>TEST-206</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>TEST-207</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>TEST-208</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>URS-050</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>The door from the CNC Washroom to the first airlock (Gowning Room 606) shall be accessed by authorized personnel (align with existing security system).</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Access Control</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Access logs and authorization lists should be reviewed to ensure compliance with access control requirements.</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>TEST-209</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>TEST-210</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>TEST-211</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>TEST-212</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>TEST-213</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>TEST-214</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>URS-051</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>The interior doors of the gowning airlock and the material/equipment airlock shall be interlocked.</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Safety and Compliance</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Interlock functionality must be tested to ensure that doors cannot be opened simultaneously.</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>TEST-215</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>TEST-216</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>TEST-217</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>TEST-218</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>TEST-219</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>TEST-220</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>URS-052</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>After opening one door, the subsequent doors shall be interlocked.</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Safety and Security</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Interlock functionality must be tested to ensure that subsequent doors cannot be opened until the previous door is closed.</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>TEST-221</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>TEST-222</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>TEST-223</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>TEST-224</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>TEST-225</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>TEST-226</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>URS-053</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Once all doors are closed, a differential pressure setpoint shall come into range before another door shall be opened.</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Operational Control</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Ensure that differential pressure setpoint is achieved before door operation.</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>TEST-227</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>TEST-228</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>TEST-229</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>TEST-230</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>TEST-231</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>TEST-232</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>URS-054</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>All doors shall be equipped with panic locks as required by NFPA and building code.</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Safety and Security</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Ensure panic locks are installed and functional as per NFPA and building code requirements.</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>TEST-233</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>TEST-234</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>TEST-235</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>URS-055</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>The doors shall be unlocked via a tamper-proof emergency push button (on both sides of the escape door).</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Safety and Security</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Ensure that the emergency push button is tamper-proof and functions correctly from both sides of the escape door.</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>TEST-236</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>TEST-237</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>TEST-238</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>URS-056</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>The opening of all doors shall also work in the event of a power outage.</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Operational Continuity</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Functional testing during power outage scenarios to ensure doors can be opened manually or through backup systems.</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>TEST-239</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>TEST-240</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>TEST-241</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>URS-057</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>The airlock control components shall be visible from the cleanroom wall.</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Facility Design</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Visual inspection of airlock control components from the cleanroom wall to ensure cleanliness and functionality.</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>TEST-242</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>TEST-243</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>TEST-244</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>TEST-245</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>URS-058</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Piping routes inside the cleanroom area shall be kept short and installed vertically wherever possible.</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Design Requirement</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Ensure that piping routes are designed and installed according to the specified requirements.</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>TEST-246</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>TEST-247</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>TEST-248</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>URS-059</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>When needed, brackets shall be used such that the piping is kept away from the wall.</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Equipment Installation</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Visual inspection and measurement of distance from wall to piping.</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>TEST-249</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>TEST-250</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>TEST-251</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>URS-060</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>The furniture in the airlocks shall be made of stainless steel where it is possible.</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Material Compliance</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Material specifications and compliance with GMP standards must be verified during design qualification.</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>TEST-252</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>TEST-253</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>TEST-254</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>URS-061</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>All other fittings shall be cleanroom compatible.</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Equipment Compatibility</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Visual inspection and cleaning validation results.</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>TEST-255</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>TEST-256</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>TEST-257</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>TEST-258</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>URS-062</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>For electrical and signal cables, empty conduits shall be integrated into the wall panels or into the door structures.</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Infrastructure and Utilities</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Ensure that conduits are properly integrated to prevent interference with electrical and signal integrity.</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>TEST-259</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>TEST-260</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>TEST-261</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>TEST-262</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>TEST-263</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>TEST-264</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>TEST-265</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>URS-063</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>All surfaces shall be cleanable (wipe cleaning), flat and smooth, sealed, and abrasion-resistant.</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Cleaning and Maintenance</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Cleaning validation and effectiveness confirmation</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>TEST-266</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>TEST-267</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>TEST-268</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>TEST-269</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>URS-064</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>The Washroom (Room 605) shall have Purified Water POU.</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Utility Qualification</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Ensure that the Purified Water Point of Use (POU) system meets the specified design and operational requirements.</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>TEST-270</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>TEST-271</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>TEST-272</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>TEST-273</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>TEST-274</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>TEST-275</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>TEST-276</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>URS-065</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>The Glassware Package Room (Room 609) shall have electrical outlets.</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Utilities</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Ensure electrical outlets are installed and functioning properly.</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>TEST-277</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>TEST-278</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>TEST-279</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>TEST-280</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>TEST-281</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>TEST-282</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>TEST-283</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>URS-066</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Electricity shall be provided in all rooms.</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Utility Requirement</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Ensure consistent and reliable electricity supply to all rooms to support equipment operation and environmental controls.</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>TEST-284</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>TEST-285</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>TEST-286</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>TEST-287</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>TEST-288</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>TEST-289</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>TEST-290</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>URS-067</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>The light inside the cleanroom and material/gowning airlocks shall be provided with a dedicated light switch inside each space.</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Facility Design</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Visual inspection and functional testing of light switches.</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>TEST-291</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>TEST-292</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>TEST-293</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>TEST-294</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>URS-068</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>The clean room area including airlocks shall be provided with low voltage lighting control system.</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Facility Design and Control</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>The low voltage lighting control system must be verified to ensure it operates effectively within the clean room environment.</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>TEST-295</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>TEST-296</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>TEST-297</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>TEST-298</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>URS-069</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>All graded rooms shall have a DicksonOne monitoring instrument.</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Monitoring Equipment</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Ensure continuous monitoring of environmental conditions in graded rooms.</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>TEST-299</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>TEST-300</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>TEST-301</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>TEST-302</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>TEST-303</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>TEST-304</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>TEST-305</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>URS-001</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>The laboratory shall comply with, but not be limited to, the following regulations and guidelines:</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Regulatory Compliance</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Ensure that all electronic records and signatures comply with 21 CFR Part 11 requirements.</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>TEST-306</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>TEST-307</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>TEST-308</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>TEST-309</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>TEST-310</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>TEST-311</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>URS-002</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>UR1 | Laboratory shall be at least 250 square feet and not more than 1000 square feet. | Medium | Provides sufficient space for up to two biosafety cabinets, three incubators, one refrigerator, and adequate bench space while minimizing unnecessary footprint</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Facility Design</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Ensure the laboratory space meets the specified dimensions and layout requirements.</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>TEST-312</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>TEST-313</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>TEST-314</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>URS-003</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>UR2 | Laboratory must 1-2 entrances/exits. | An entrance/exit is required for use of the room.</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Facility Design</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Ensure that the design includes 1-2 entrances/exits as specified in the URS.</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>TEST-315</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr"/>
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>TEST-316</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>TEST-317</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>URS-004</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>UR | Critical activities shall be performed in qualified biosafety cabinets or laminar airflow hoods | High | Ensures appropriate aseptic environments to maintain sample integrity and contamination prevention.</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Environmental Control</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Ensure that biosafety cabinets or laminar airflow hoods are qualified and maintained according to established protocols.</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>TEST-318</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>TEST-319</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>TEST-320</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>TEST-321</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>TEST-322</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>URS-005</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>UR | Room shall | High | Minimizes cross-contamination and supports GMP best practices.</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Facility Design</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Risk assessment and validation of cleaning procedures and HVAC systems.</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>TEST-323</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>TEST-324</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>TEST-325</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>TEST-326</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>TEST-327</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>TEST-328</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>URS-006</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>UR | Temperature shall be maintained between 15-25°C with monitoring and alarms | Medium | Supports equipment function, personnel comfort, and consistent test conditions.</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Environmental Control</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Temperature monitoring system must be validated to ensure it operates within specified limits.</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>TEST-329</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>TEST-330</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>TEST-331</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>TEST-332</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>TEST-333</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>TEST-334</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>TEST-335</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>URS-007</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>UR | Relative humidity shall be monitored</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Environmental Monitoring</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Continuous monitoring with alarms for deviations</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>TEST-336</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>TEST-337</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>TEST-338</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>TEST-339</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>TEST-340</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>URS-008</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>UR | Ceilings shall be non-porous. | Medium | Prevents harbouring of microbes.</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Facility Design</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Visual inspection and microbial testing of surfaces.</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>TEST-341</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>TEST-342</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>TEST-343</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>TEST-344</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>URS-009</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>UR | Flooring shall be compatible to support the use of detergents and disinfectants that are necessary for cleaning. | High | Facilitates effective cleaning and disinfection.</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Facility Design</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Cleaning validation and effectiveness testing of the flooring material.</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>TEST-345</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr"/>
+      <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>TEST-346</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>TEST-347</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>TEST-348</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>URS-010</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>UR1 | Door(s) shall be self-closing | Medium | Helps maintain</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Facility Design</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Visual inspection and functional testing of door operation.</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>TEST-349</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>TEST-350</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>TEST-351</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>URS-011</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>UR1 | Windows shall be included in doors. | Low | Allows visibility into the lab, reducing unnecessary entry.</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Facility Design</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Visual inspection of the installed doors to confirm the presence of windows.</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>TEST-352</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr"/>
+      <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>TEST-353</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>TEST-354</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>URS-012</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>UR1 | Safety signage shall be posted as appropriate | Communicates hazards and required behaviors to personnel.</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Safety and Compliance</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Ensure that safety signage is visible, legible, and appropriately placed in all relevant areas.</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="inlineStr"/>
+      <c r="H82" t="inlineStr"/>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>TEST-355</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>URS-013</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>UR | Biohazard waste shall be segregated | Medium | Prevents contamination.</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Biohazard Waste Management</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Regular audits and inspections of waste segregation practices.</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr"/>
+      <c r="G83" t="inlineStr"/>
+      <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>TEST-356</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>URS-014</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>UR | Countertops shall be constructed of non-porous, chemical-resistant, and cleanable materials (e.g., epoxy resin, phenolic resin, or stainless steel). | Prevents absorption of contaminants and supports effective cleaning and disinfection.</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Material Specification</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Material testing and cleaning validation</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>TEST-357</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr"/>
+      <c r="H84" t="inlineStr"/>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>TEST-358</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>TEST-359</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>TEST-360</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>URS-015</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>UR | Shelving shall be constructed of cleanable, and designed to minimize dust accumulation (e.g. enclosed cabinets). | Medium | Reduces particulate and microbial contamination risks and supports housekeeping.</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Facility Design</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Visual inspection and cleaning validation results.</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>TEST-361</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr"/>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>TEST-362</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>TEST-363</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>TEST-364</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>TEST-365</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
